--- a/태양광 결과.xlsx
+++ b/태양광 결과.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB23E32-B24D-4A54-875C-4C9CDD9AB507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E18787-1765-4B9E-98EF-1129A622246F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -155,6 +155,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -568,13 +571,13 @@
       <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>13386344829</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="6">
         <v>387617131</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>49617213</v>
       </c>
     </row>
@@ -583,13 +586,13 @@
       <c r="B7" t="s">
         <v>0</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6">
         <v>25659536183</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="6">
         <v>749184769</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="6">
         <v>322267615</v>
       </c>
     </row>
@@ -600,14 +603,14 @@
       <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>12929442989</v>
       </c>
-      <c r="D8">
-        <v>385028533</v>
-      </c>
-      <c r="E8">
-        <v>38547333</v>
+      <c r="D8" s="6">
+        <v>365534473</v>
+      </c>
+      <c r="E8" s="6">
+        <v>34632200</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -615,13 +618,13 @@
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>24774551104</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="6">
         <v>706305918</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <v>290482244</v>
       </c>
     </row>
@@ -632,14 +635,14 @@
       <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <v>456901840</v>
       </c>
-      <c r="D10">
-        <v>22161078</v>
-      </c>
-      <c r="E10">
-        <v>15039027</v>
+      <c r="D10" s="6">
+        <v>22082658</v>
+      </c>
+      <c r="E10" s="6">
+        <v>14985012</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
@@ -647,13 +650,13 @@
       <c r="B11" t="s">
         <v>0</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="6">
         <v>884985078</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="6">
         <v>42878850</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="6">
         <v>31785370</v>
       </c>
     </row>
@@ -689,11 +692,11 @@
       </c>
       <c r="G15" s="4">
         <f>SUM(D17,D19)</f>
-        <v>407.18961099999996</v>
+        <v>387.61713099999997</v>
       </c>
       <c r="H15" s="4">
         <f>SUM(E17,E19)</f>
-        <v>53.586359999999999</v>
+        <v>49.617211999999995</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
@@ -727,11 +730,11 @@
       </c>
       <c r="D17" s="2">
         <f t="shared" si="2"/>
-        <v>385.02853299999998</v>
+        <v>365.53447299999999</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="2"/>
-        <v>38.547333000000002</v>
+        <v>34.632199999999997</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -765,11 +768,11 @@
       </c>
       <c r="D19" s="2">
         <f t="shared" si="4"/>
-        <v>22.161078</v>
+        <v>22.082657999999999</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="4"/>
-        <v>15.039027000000001</v>
+        <v>14.985011999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">

--- a/태양광 결과.xlsx
+++ b/태양광 결과.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\GRI Github\Raster_PV_Poten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E18787-1765-4B9E-98EF-1129A622246F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF4D5A6-AB7D-4C66-9679-5B38A87FC9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,8 +78,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -156,7 +157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -181,16 +182,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>211840</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>415925</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>107065</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -213,8 +214,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6267450" y="1638300"/>
-          <a:ext cx="5140325" cy="4488565"/>
+          <a:off x="7877175" y="4819650"/>
+          <a:ext cx="5368925" cy="4298065"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -544,16 +545,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE1E31F-5612-4994-A799-8138DE6307A6}">
   <dimension ref="A3:K23"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="K3" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>5</v>
       </c>
@@ -564,103 +565,103 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>13386344829</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6">
         <v>387617131</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6">
         <v>49617213</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>25659536183</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7">
         <v>749184769</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7">
         <v>322267615</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>12929442989</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <v>365534473</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <v>34632200</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9">
         <v>24774551104</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9">
         <v>706305918</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9">
         <v>290482244</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10">
         <v>456901840</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10">
         <v>22082658</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10">
         <v>14985012</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11">
         <v>884985078</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11">
         <v>42878850</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11">
         <v>31785370</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>5</v>
       </c>
@@ -671,7 +672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>2</v>
       </c>
@@ -690,16 +691,10 @@
         <f t="shared" si="0"/>
         <v>49.617213</v>
       </c>
-      <c r="G15" s="4">
-        <f>SUM(D17,D19)</f>
-        <v>387.61713099999997</v>
-      </c>
-      <c r="H15" s="4">
-        <f>SUM(E17,E19)</f>
-        <v>49.617211999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>0</v>
@@ -716,8 +711,16 @@
         <f t="shared" si="1"/>
         <v>322.26761499999998</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F16" s="6">
+        <f>D16/D15</f>
+        <v>1.9327958159826533</v>
+      </c>
+      <c r="G16" s="6">
+        <f>E16/E15</f>
+        <v>6.4950769201809058</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>3</v>
       </c>
@@ -736,8 +739,10 @@
         <f t="shared" si="2"/>
         <v>34.632199999999997</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" t="s">
         <v>0</v>
@@ -754,8 +759,16 @@
         <f t="shared" si="3"/>
         <v>290.48224399999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F18" s="6">
+        <f>D18/D17</f>
+        <v>1.932255286904226</v>
+      </c>
+      <c r="G18" s="6">
+        <f>E18/E17</f>
+        <v>8.3876347445440942</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>4</v>
       </c>
@@ -774,8 +787,10 @@
         <f t="shared" si="4"/>
         <v>14.985011999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" t="s">
         <v>0</v>
@@ -792,8 +807,16 @@
         <f t="shared" si="5"/>
         <v>31.78537</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="F20" s="6">
+        <f>D20/D19</f>
+        <v>1.9417431542887638</v>
+      </c>
+      <c r="G20" s="6">
+        <f>E20/E19</f>
+        <v>2.1211441138652409</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
         <v>8</v>
       </c>

--- a/태양광 결과.xlsx
+++ b/태양광 결과.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\GRI Github\Raster_PV_Poten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF4D5A6-AB7D-4C66-9679-5B38A87FC9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8611587E-BD91-4985-BB4C-DEA2B2C9F069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{1AF8F648-50C3-4598-AF8B-CDC22DD09268}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>NIMS</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -71,6 +71,34 @@
   </si>
   <si>
     <t>1500짜리 지상형과 옥상형의 합이 전체와 맞지 않음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이론적</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술적</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>총합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥상형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단위: TWh</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -80,7 +108,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -145,19 +173,19 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -189,7 +217,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>415925</xdr:colOff>
+      <xdr:colOff>263525</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>107065</xdr:rowOff>
     </xdr:to>
@@ -544,17 +572,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE1E31F-5612-4994-A799-8138DE6307A6}">
-  <dimension ref="A3:K23"/>
+  <dimension ref="A3:Q23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K3" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>5</v>
       </c>
@@ -564,8 +607,23 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N5" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="3">
+        <f>SUM(O6:O7)</f>
+        <v>13386.344829</v>
+      </c>
+      <c r="P5" s="3">
+        <f t="shared" ref="P5:Q5" si="0">SUM(P6:P7)</f>
+        <v>387.61713099999997</v>
+      </c>
+      <c r="Q5" s="3">
+        <f t="shared" si="0"/>
+        <v>49.617211999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>2</v>
       </c>
@@ -581,8 +639,23 @@
       <c r="E6">
         <v>49617213</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="3">
+        <f>C17</f>
+        <v>12929.442988999999</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" ref="P6:Q6" si="1">D17</f>
+        <v>365.53447299999999</v>
+      </c>
+      <c r="Q6" s="3">
+        <f t="shared" si="1"/>
+        <v>34.632199999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>0</v>
@@ -596,8 +669,23 @@
       <c r="E7">
         <v>322267615</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="N7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="3">
+        <f>C19</f>
+        <v>456.90183999999999</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" ref="P7:Q7" si="2">D19</f>
+        <v>22.082657999999999</v>
+      </c>
+      <c r="Q7" s="3">
+        <f t="shared" si="2"/>
+        <v>14.985011999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
@@ -614,7 +702,7 @@
         <v>34632200</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" t="s">
         <v>0</v>
@@ -629,7 +717,7 @@
         <v>290482244</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
@@ -646,7 +734,7 @@
         <v>14985012</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" t="s">
         <v>0</v>
@@ -661,7 +749,7 @@
         <v>31785370</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>5</v>
       </c>
@@ -672,7 +760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>2</v>
       </c>
@@ -683,39 +771,39 @@
         <f>C6/10^(6)</f>
         <v>13386.344829</v>
       </c>
-      <c r="D15" s="2">
-        <f t="shared" ref="D15:E15" si="0">D6/10^(6)</f>
+      <c r="D15" s="6">
+        <f t="shared" ref="D15:E15" si="3">D6/10^(6)</f>
         <v>387.61713099999997</v>
       </c>
-      <c r="E15" s="2">
-        <f t="shared" si="0"/>
+      <c r="E15" s="6">
+        <f t="shared" si="3"/>
         <v>49.617213</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" ref="C16:E16" si="1">C7/10^(6)</f>
+        <f t="shared" ref="C16:E16" si="4">C7/10^(6)</f>
         <v>25659.536183</v>
       </c>
-      <c r="D16" s="1">
-        <f t="shared" si="1"/>
+      <c r="D16" s="6">
+        <f t="shared" si="4"/>
         <v>749.18476899999996</v>
       </c>
-      <c r="E16" s="1">
-        <f t="shared" si="1"/>
+      <c r="E16" s="6">
+        <f t="shared" si="4"/>
         <v>322.26761499999998</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="4">
         <f>D16/D15</f>
         <v>1.9327958159826533</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="4">
         <f>E16/E15</f>
         <v>6.4950769201809058</v>
       </c>
@@ -728,19 +816,19 @@
         <v>1</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" ref="C17:E17" si="2">C8/10^(6)</f>
+        <f t="shared" ref="C17:E17" si="5">C8/10^(6)</f>
         <v>12929.442988999999</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="2"/>
+      <c r="D17" s="6">
+        <f t="shared" si="5"/>
         <v>365.53447299999999</v>
       </c>
-      <c r="E17" s="2">
-        <f t="shared" si="2"/>
+      <c r="E17" s="6">
+        <f t="shared" si="5"/>
         <v>34.632199999999997</v>
       </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
@@ -748,22 +836,22 @@
         <v>0</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" ref="C18:E18" si="3">C9/10^(6)</f>
+        <f t="shared" ref="C18:E18" si="6">C9/10^(6)</f>
         <v>24774.551103999998</v>
       </c>
-      <c r="D18" s="1">
-        <f t="shared" si="3"/>
+      <c r="D18" s="6">
+        <f t="shared" si="6"/>
         <v>706.30591800000002</v>
       </c>
-      <c r="E18" s="1">
-        <f t="shared" si="3"/>
+      <c r="E18" s="6">
+        <f t="shared" si="6"/>
         <v>290.48224399999998</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="4">
         <f>D18/D17</f>
         <v>1.932255286904226</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="4">
         <f>E18/E17</f>
         <v>8.3876347445440942</v>
       </c>
@@ -776,19 +864,19 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" ref="C19:E19" si="4">C10/10^(6)</f>
+        <f t="shared" ref="C19:E19" si="7">C10/10^(6)</f>
         <v>456.90183999999999</v>
       </c>
-      <c r="D19" s="2">
-        <f t="shared" si="4"/>
+      <c r="D19" s="6">
+        <f t="shared" si="7"/>
         <v>22.082657999999999</v>
       </c>
-      <c r="E19" s="2">
-        <f t="shared" si="4"/>
+      <c r="E19" s="6">
+        <f t="shared" si="7"/>
         <v>14.985011999999999</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
@@ -796,22 +884,22 @@
         <v>0</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" ref="C20:E20" si="5">C11/10^(6)</f>
+        <f t="shared" ref="C20:E20" si="8">C11/10^(6)</f>
         <v>884.98507800000004</v>
       </c>
-      <c r="D20" s="1">
-        <f t="shared" si="5"/>
+      <c r="D20" s="6">
+        <f t="shared" si="8"/>
         <v>42.87885</v>
       </c>
-      <c r="E20" s="1">
-        <f t="shared" si="5"/>
+      <c r="E20" s="6">
+        <f t="shared" si="8"/>
         <v>31.78537</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="4">
         <f>D20/D19</f>
         <v>1.9417431542887638</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="4">
         <f>E20/E19</f>
         <v>2.1211441138652409</v>
       </c>
